--- a/artfynd/A 24799-2024 artfynd.xlsx
+++ b/artfynd/A 24799-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,121 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128806744</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92041</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>760</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Marktjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>558651</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6944956</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Känd förekomst.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Britta Sterner, Linus Söderquist, Agnes  Blomgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 24799-2024 artfynd.xlsx
+++ b/artfynd/A 24799-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128806744</v>
       </c>
       <c r="B3" t="n">
-        <v>92041</v>
+        <v>92068</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24799-2024 artfynd.xlsx
+++ b/artfynd/A 24799-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128806744</v>
       </c>
       <c r="B3" t="n">
-        <v>92068</v>
+        <v>92073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24799-2024 artfynd.xlsx
+++ b/artfynd/A 24799-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128806744</v>
       </c>
       <c r="B3" t="n">
-        <v>92073</v>
+        <v>92078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24799-2024 artfynd.xlsx
+++ b/artfynd/A 24799-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128806744</v>
       </c>
       <c r="B3" t="n">
-        <v>92078</v>
+        <v>92082</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24799-2024 artfynd.xlsx
+++ b/artfynd/A 24799-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128806744</v>
       </c>
       <c r="B3" t="n">
-        <v>92082</v>
+        <v>92087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24799-2024 artfynd.xlsx
+++ b/artfynd/A 24799-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128806744</v>
       </c>
       <c r="B3" t="n">
-        <v>92095</v>
+        <v>92100</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24799-2024 artfynd.xlsx
+++ b/artfynd/A 24799-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128806744</v>
       </c>
       <c r="B3" t="n">
-        <v>92100</v>
+        <v>92103</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24799-2024 artfynd.xlsx
+++ b/artfynd/A 24799-2024 artfynd.xlsx
@@ -895,7 +895,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Britta Sterner, Linus Söderquist, Agnes  Blomgren</t>
+          <t>Agnes  Blomgren, Linus Söderquist, Britta Sterner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 24799-2024 artfynd.xlsx
+++ b/artfynd/A 24799-2024 artfynd.xlsx
@@ -895,7 +895,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Agnes  Blomgren, Linus Söderquist, Britta Sterner</t>
+          <t>Britta Sterner, Linus Söderquist, Agnes  Blomgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 24799-2024 artfynd.xlsx
+++ b/artfynd/A 24799-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128806744</v>
       </c>
       <c r="B3" t="n">
-        <v>92103</v>
+        <v>92110</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24799-2024 artfynd.xlsx
+++ b/artfynd/A 24799-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128806744</v>
       </c>
       <c r="B3" t="n">
-        <v>92110</v>
+        <v>92117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24799-2024 artfynd.xlsx
+++ b/artfynd/A 24799-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128806744</v>
       </c>
       <c r="B3" t="n">
-        <v>92117</v>
+        <v>92119</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24799-2024 artfynd.xlsx
+++ b/artfynd/A 24799-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128806744</v>
       </c>
       <c r="B3" t="n">
-        <v>92119</v>
+        <v>92134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24799-2024 artfynd.xlsx
+++ b/artfynd/A 24799-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128806744</v>
       </c>
       <c r="B3" t="n">
-        <v>92134</v>
+        <v>92135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Britta Sterner, Linus Söderquist, Agnes  Blomgren</t>
+          <t>Agnes  Blomgren, Linus Söderquist, Britta Sterner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
